--- a/data/trans_orig/P21D_5_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D_5_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199405</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137485</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>340604</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1073,97 +1073,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2689</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>924</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4736</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5832</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4448</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>286383</t>
+          <t>285230</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>491393</t>
+          <t>490009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,97 +1416,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3246</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>741</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4456</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3906</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3758</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213632</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>253233</t>
+          <t>254443</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>469417</t>
+          <t>469269</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>520122</t>
+          <t>518210</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>316788</t>
+          <t>316709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>839641</t>
+          <t>840223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232446</t>
+          <t>232561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>221575</t>
+          <t>221634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>226116</t>
+          <t>226114</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>456732</t>
+          <t>456404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>463924</t>
+          <t>463922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181896</t>
+          <t>181973</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185114</t>
+          <t>185115</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>338339</t>
+          <t>338226</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>341470</t>
+          <t>341469</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,62 +2823,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115086</t>
+          <t>115396</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>169103</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>285038</t>
+          <t>284661</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1654702</t>
+          <t>1654386</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1662825</t>
+          <t>1662916</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1580255</t>
+          <t>1580377</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1589150</t>
+          <t>1589055</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3240081</t>
+          <t>3239555</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3251006</t>
+          <t>3250484</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_5_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D_5_R-Edad-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>987</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>987</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>290195</t>
+          <t>249367</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>285230</t>
+          <t>245322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>494917</t>
+          <t>476179</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>490009</t>
+          <t>472720</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>810</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>810</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>256948</t>
+          <t>295825</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254443</t>
+          <t>292635</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>472434</t>
+          <t>548343</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>469269</t>
+          <t>545591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>525280</t>
+          <t>314767</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>518210</t>
+          <t>309539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>526394</t>
+          <t>315912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>319528</t>
+          <t>344441</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>316709</t>
+          <t>341007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>844808</t>
+          <t>659208</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>840223</t>
+          <t>654265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>847256</t>
+          <t>661040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>526394</t>
+          <t>315912</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>526394</t>
+          <t>315912</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>526394</t>
+          <t>315912</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>847256</t>
+          <t>661720</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>847256</t>
+          <t>661720</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>847256</t>
+          <t>661720</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,92 +2107,92 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5154</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>3616</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>8544</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5058</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>3543</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>8792</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2210,102 +2210,102 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>236807</t>
+          <t>255827</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232561</t>
+          <t>250622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>251491</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>248299</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>252840</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,97%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>507318</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>502390</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>509655</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>224846</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>221634</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>226114</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>461653</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>456404</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>463922</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>385</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>184184</t>
+          <t>197428</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181973</t>
+          <t>194737</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185115</t>
+          <t>198597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>340538</t>
+          <t>371482</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>338226</t>
+          <t>368512</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>341469</t>
+          <t>372650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>117636</t>
+          <t>128975</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115396</t>
+          <t>126379</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2966,27 +2966,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>287686</t>
+          <t>315134</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>284661</t>
+          <t>312782</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,67 +3126,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>12548</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2979</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>11657</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -3239,69 +3239,69 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1660233</t>
+          <t>1563733</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1654386</t>
+          <t>1558544</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1662916</t>
+          <t>1566129</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,94%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2362</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1687695</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1681826</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1691005</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,96%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2362</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1586096</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1580377</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1589055</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>3817</t>
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3246329</t>
+          <t>3251428</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3239555</t>
+          <t>3244752</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3250484</t>
+          <t>3255790</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1663614</t>
+          <t>1567118</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3255648</t>
+          <t>3261492</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
